--- a/data/legado-solides/samples/colaboradores_min.xlsx
+++ b/data/legado-solides/samples/colaboradores_min.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Colaboradores" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -46,8 +46,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,168 +463,183 @@
           <t>Superior direto id</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>CPF</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Unidade</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ana Silva</t>
+          <t>Gestor Alpha</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ana.silva@example.com</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+          <t>gestor.alpha@example.com</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Desenvolvedor</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
+          <t>Tech Lead Fixture</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>9004</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Engenharia</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>Engenharia Fixture</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>000.000.000-00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bruno Costa</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>bruno.costa@example.com</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>Ana Silva</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ana.silva@example.com</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Analista</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
+          <t>Desenvolvedor Fixture</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>9001</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Produto</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>Engenharia Fixture</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>000.000.000-00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Carla Dias</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>carla.dias@example.com</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="n">
-        <v>45446</v>
+          <t>Bruno Costa</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>bruno.costa@example.com</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Desenvolvedor</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
+          <t>Analista Fixture</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>9002</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Engenharia</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Produto Fixture</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>100</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>000.000.000-00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Diego Alves</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>diego.alves@example.com</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2024-06-01</t>
-        </is>
+          <t>Carla Dias</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>carla.dias@example.com</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>45446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Analista</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
+          <t>Desenvolvedor Fixture</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>9001</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Produto</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>Engenharia Fixture</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>000.000.000-00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Elena Sem Email</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+          <t>Diego Alves</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>diego.alves@example.com</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>2024-06-01</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Estagiario</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>Analista Fixture</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>9002</v>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>RH</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Produto Fixture</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>100</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>000.000.000-00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -636,54 +652,76 @@
           <t>fernanda.lima@example.com</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>People Partner</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
+          <t>People Partner Fixture</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>9003</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>RH</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>RH Fixture</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>000.000.000-00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Gestor Alpha</t>
+          <t>Nome Ambiguo</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>gestor.alpha@example.com</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+          <t>nome.ambiguo@example.com</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tech Lead</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>C4</t>
-        </is>
+          <t>Analista Fixture</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>9002</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Engenharia</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Produto Fixture</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>000.000.000-00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Elena Sem Email</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Estagiario Fixture</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>RH Fixture</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>000.000.000-00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
